--- a/docs/vorlagen/testfall-import-vorlage.xlsx
+++ b/docs/vorlagen/testfall-import-vorlage.xlsx
@@ -485,7 +485,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Zielsystem: SAP S/4HANA 2025 (Releasezyklus mit Feature Pack Stacks). Die Codes in den Auswahllisten stammen aus dem Mockup; Kunden-, Geräte- und Belegdaten sind fiktiv.</t>
+          <t>Zielsystem: SAP S/4HANA 2025 (Releasezyklus mit Feature Package Stacks). Die Codes in den Auswahllisten stammen aus dem Mockup; Kunden-, Geräte- und Belegdaten sind fiktiv.</t>
         </is>
       </c>
     </row>
